--- a/code/experiment/256chunk_BGE-M3_5topk_Y.xlsx
+++ b/code/experiment/256chunk_BGE-M3_5topk_Y.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rag_project\code\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rag_project\code\experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FFD4868-4DB0-4A52-AD08-278D77D57317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C786848-6F2C-4315-9757-88C527CA70F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -86,48 +86,28 @@
     <t>作者将post-training scaling分为三个主要方法：Supervised Fine-tuning (SFT), Reinforcement Learning (RLxF), and Test-time Compute (TTC).</t>
   </si>
   <si>
-    <t>作者将post-training scaling分为三个主要方法：监督微调（Supervised Fine-tuning, SFT）、强化学习（Reinforcement Learning, RL）和测试时计算（Test-time Compute, TTC）。
-来自: [2025.acl-long.140_A Survey of Post-Training Scaling in Large Language Models, 第2页, 2025.acl-long.140_A Survey of Post-Training Scaling in Large Language Models_chunk_008]</t>
-  </si>
-  <si>
     <t>在SafeRAG中"silver noise"的定义是什么？</t>
   </si>
   <si>
     <t>首先，我们定义了“银色噪声”，它指的是仅部分包含答案的证据文本。此类噪声能够绕过大多数安全过滤机制，从而削弱 RAG 的多样性。</t>
   </si>
   <si>
-    <t>Silver noise是指部分包含答案的证据。
-来自: [2025.acl-long.230_SafeRAG, 第2页, 2025.acl-long.230_SafeRAG_chunk_007]</t>
-  </si>
-  <si>
     <t>RAG噪声被分为哪两类？</t>
   </si>
   <si>
     <t>RAG噪声被分为有益噪声和有害噪声。</t>
   </si>
   <si>
-    <t>RAG噪声被分为有益噪声和有害噪声两类。
-来自: [2025.acl-long.250_Pandora s Box or Aladdin s Lamp, 第2页, 2025.acl-long.250_Pandora s Box or Aladdin s Lamp_chunk_006]</t>
-  </si>
-  <si>
     <t>什么是Ref-Long基准？它评估的是长上下文语言模型的什么能力？</t>
   </si>
   <si>
     <t>Ref-Long是一个专门设计用于评估长上下文语言模型（LCLMs）长上下文引用能力的基准。它要求LCLMs不仅要在给定文档中识别特定关键词，还要找出引用该关键词的文档索引，而不是其他相关但不匹配的文档。</t>
   </si>
   <si>
-    <t>Ref-Long是一个专门设计用于评估长上下文语言模型的长上下文引用能力的基准。
-来自: [2025.acl-long.1162_Ref-Long, 第1页, 2025.acl-long.1162_Ref-Long_chunk_001]</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 什么是SYNQA方法？</t>
   </si>
   <si>
     <t>SYNQA 是一种生成式上下文归因数据合成方法。核心思路是：给定选定的上下文句子，由大语言模型（LLM）生成完全受这些句子支持的问题-答案对（QA对）。该方法能够产生反映真实世界多样化问答场景的训练数据，帮助模型学习稳健的归因能力。SYNQA 同时生成以实体为中心和以对话为中心的样本，从而提升模型在不同上下文和领域的泛化能力。</t>
-  </si>
-  <si>
-    <t>SYNQA是一种生成式方法，给定选定的上下文句子，由大语言模型生成完全由这些句子支持的问答对。
-来自: [2025.acl-long.828_On Synthesizing Data for Context Attribution in Question Answering, 第2页, 2025.acl-long.828_On Synthesizing Data for Context Attribution in Question Answering_chunk_009]</t>
   </si>
   <si>
     <t>什么是Agentic Long-Context Understanding (AgenticLU)框架？</t>
@@ -137,70 +117,42 @@
 </t>
   </si>
   <si>
-    <t>AgenticLU是一个通过将目标自澄清与上下文接地整合到智能体工作流中来增强大语言模型对长上下文查询理解的框架。
-来自: [2025.acl-long.275_Self-Taught Agentic Long Context Understanding, 第1页, 2025.acl-long.275_Self-Taught Agentic Long Context Understanding_chunk_001]</t>
-  </si>
-  <si>
     <t>什么是Agentic Reasoning框架?</t>
   </si>
   <si>
     <t>Agentic Reasoning是一个通过集成外部工具使用代理来增强大型语言模型推理的框架。</t>
   </si>
   <si>
-    <t>Agentic Reasoning 是一个通过将外部基于LLM的智能体作为工具集成到推理过程中，从而增强大语言模型推理能力的框架。
-来自: [2025.acl-long.1383_Agentic Reasoning, 第2页, 2025.acl-long.1383_Agentic Reasoning_chunk_008]</t>
-  </si>
-  <si>
     <t>REAL-MM-RAG 基准测试旨在解决现实世界检索的四个关键属性是什么？</t>
   </si>
   <si>
     <t xml:space="preserve"> REAL-MM-RAG基准测试的四个关键属性是：(i) 多模态文档，(ii) 增强的难度，(iii) 真实的RAG查询，(iv) 准确的标注。</t>
   </si>
   <si>
-    <t>REAL-MM-RAG 基准测试旨在解决的四个关键属性是：(i) 多模态文档（包含文本、图表、表格等视觉元素）；(ii) 增强难度（需要超越简单关键词匹配，在上下文相似的页面中进行挑战性评估）；(iii) 真实 RAG 查询（问题自然提出，不显式引用页面，反映真实检索场景）；(iv) 准确标注（所有相关文档必须被正确且穷尽地标注，以避免低估检索性能并防止假阴性）。
-来自: [2025.acl-long.1528_REAL-MM-RAG, 第1页, 2025.acl-long.1528_REAL-MM-RAG_chunk_003]</t>
-  </si>
-  <si>
     <t>ASTUTE RAG的定义是什么？有什么用?</t>
   </si>
   <si>
     <t>为了使大语言模型对不完美的检索结果更具鲁棒性，我们提出了 ASTUTE RAG，这是一种新颖的检索增强生成方法。该方法能够自适应地从大语言模型的内部知识中提取关键信息，在感知信息来源的基础上迭代整合内外部知识，并根据信息的可靠性最终生成答案。</t>
   </si>
   <si>
-    <t>ASTUTE RAG是一种新颖的检索增强生成方法，旨在对不完美的检索增强具有鲁棒性，同时保留可靠检索时的 grounding 效果。它用于缓解不完美检索增强的影响，解决LLM内部知识与外部知识之间的冲突，从而生成更准确可靠的响应。
-来自: [2025.acl-long.1476_Astute RAG, 第2页, 2025.acl-long.1476_Astute RAG_chunk_007] 和 [2025.acl-long.1476_Astute RAG, 第4页, 2025.acl-long.1476_Astute RAG_chunk_016]</t>
-  </si>
-  <si>
     <t>L-CiteEval的定义是什么？</t>
   </si>
   <si>
     <t>L-CiteEval是一个开箱即用的评估套件，用于评估长上下文模型（LCMs）的生成质量和保真度。它包含两个关键组件：（1）一个涵盖5大任务类别和11个多样化长上下文任务的综合基准测试，上下文长度从8K到48K；（2）相应的自动评估指标和验证流程，以确保稳健可靠的评估。该套件要求模型生成陈述及其支持证据（引用），从而能够有效区分不同模型在保真度方面的差异。</t>
   </si>
   <si>
-    <t>L-CiteEval是一个开箱即用的评估套件，包含多任务长上下文基准和相应的评估流程。
-来自: [2025.acl-long.263_L-CiteEval, 第8页, 2025.acl-long.263_L-CiteEval_chunk_056]</t>
-  </si>
-  <si>
     <t xml:space="preserve"> LongBench v2基准测试包含多少个问题？上下文长度范围是多少？</t>
   </si>
   <si>
     <t>LongBench v2包含503个具有挑战性的多项选择题，上下文长度范围从8,000到200万个单词。</t>
   </si>
   <si>
-    <t>LongBench v2 包含 503 个多项选择题，上下文长度范围从 8k 到 2M 词。
-来自: [2025.acl-long.183_LongBench v2, 第1页, 2025.acl-long.183_LongBench v2_chunk_004]</t>
-  </si>
-  <si>
     <t>RHIO框架的三个主要组成部分是什么？</t>
   </si>
   <si>
     <t>RHIO框架包含三个主要组件：1.不忠实数据增强, 2.忠实度感知调优, 3.自诱导解码</t>
   </si>
   <si>
-    <t>RHIO框架的三个主要组成部分是：不忠实数据增强（unfaithful data augmentation）、忠实性感知调优（faithfulness-aware tuning）和自诱导解码（self-induced decoding）。
-来自: [2025.acl-long.826_Improving Contextual Faithfulness of Large Language Models via Retrieval Heads-Induced Optimization, 第15页, 2025.acl-long.826_Improving Contextual Faithfulness of Large Language Models via Retrieval Heads-Induced Optimization_chunk_065]</t>
-  </si>
-  <si>
     <t>在How to Train Long-Context Language Models中的监督微调（SFT）阶段，论文作者发现使用哪种类型的数据集能够在长上下文任务上取得最佳性能？</t>
   </si>
   <si>
@@ -208,10 +160,6 @@
   </si>
   <si>
     <t>作者发现，仅使用标准的、短上下文的指令数据集（如 UltraChat）进行微调，就能在长上下文任务上取得最佳效果。</t>
-  </si>
-  <si>
-    <t>作者发现使用标准的短上下文指令数据集（如Ultra-Chat）就足以在长上下文任务上取得良好性能，而长合成指令数据不会进一步提升性能。
-来自: [2025.acl-long.366_How to Train Long-Context Language Models (Effectively), 第2页, 2025.acl-long.366_How to Train Long-Context Language Models (Effectively)_chunk_006]</t>
   </si>
   <si>
     <t>在"Astute RAG"中，作者提出的knowledge consolidation过程包含哪三个主要步骤？</t>
@@ -223,39 +171,22 @@
 过滤无关信息：剔除与当前查询或任务不相关的冗余内容。</t>
   </si>
   <si>
-    <t>知识整合过程包含三个主要步骤：合并一致信息、识别冲突信息、过滤无关信息。
-来自: [2025.acl-long.1476_Astute RAG, 第2页, 2025.acl-long.1476_Astute RAG_chunk_007] 和 [2025.acl-long.1476_Astute RAG, 第16页, 2025.acl-long.1476_Astute RAG_chunk_046]</t>
-  </si>
-  <si>
     <t>LongRefiner 在推理时如何降低在线延迟？</t>
   </si>
   <si>
     <t>将推理分为离线阶段和在线阶段。离线阶段完成文档结构化任务，在线阶段仅处理用户查询分析和自适应精炼（输入输出仅数百个 tokens），整体延迟约为标准设置的 25%。</t>
   </si>
   <si>
-    <t>LongRefiner 将推理过程拆分为离线和在线两个阶段：离线阶段预先对语料库中的文档执行层次化结构处理，在线阶段仅需对用户查询进行分析并完成自适应精炼，从而大幅减少在线处理的输入和输出 token 数量，使整体延迟降至标准设置的约 25%。
-来自: [2025.acl-long.176_Hierarchical Document Refinement for Long-context Retrieval-augmented Generation, 第6页, 2025.acl-long.176_Hierarchical Document Refinement for Long-context Retrieval-augmented Generation_chunk_030]</t>
-  </si>
-  <si>
     <t>DRAG框架如何保护用户隐私？请描述其隐私保护机制。</t>
   </si>
   <si>
     <t>DRAG通过传输去标识化的查询和结构化知识而不是完整响应来保护用户隐私。这样可以避免传输完整的用户查询和敏感信息。</t>
   </si>
   <si>
-    <t>DRAG框架通过本地模型在将查询上传到云端之前重新表述或剥离敏感信息，确保隐私数据不离开本地；云端模型仅处理清理后的查询并返回证据和知识图谱，本地模型再生成最终答案。
-来自: [2025.acl-long.358_DRAG, 第1页, 2025.acl-long.358_DRAG_chunk_004]
-来自: [2025.acl-long.358_DRAG, 第5页, 2025.acl-long.358_DRAG_chunk_025]</t>
-  </si>
-  <si>
     <t>简述 Think&amp; Cite 框架中 SG-MCTS 的工作流程及其步骤。</t>
   </si>
   <si>
     <t>SG-MCTS利用LLMs的自反思能力来推理MCTS的中间状态，以指导树扩展过程。在每次迭代中，SG-MCTS 遵循四个步骤，即选择、反思引导的扩展、评估和反向传播。</t>
-  </si>
-  <si>
-    <t>SG-MCTS 在每次迭代中依次执行四个步骤：选择（selection）、反思引导的扩展（reflection-guided expansion）、评估（evaluation）和反向传播（backpropagation）。
-来自: [2025.acl-long.490_Think&amp;Cite, 第3页, 2025.acl-long.490_Think&amp;Cite_chunk_014]</t>
   </si>
   <si>
     <t>SETR 的段落选择提示（Passage Selection Prompt）所引导的关键过程包含哪三个具体步骤？每个步骤的核心任务是什么？</t>
@@ -267,38 +198,19 @@
 选择最优段落子集： 核心任务是从候选段落中挑选出一个子集，使其在整体上能提供最全面且多样化的信息覆盖，从而有效回答查询。</t>
   </si>
   <si>
-    <t>SETR 的段落选择提示引导的三个关键步骤是：(1) 列举回答查询所需的关键信息需求；(2) 为每个需求识别包含相关信息的段落；(3) 选择一组段落，这些段落共同提供最全面和多样化的覆盖，以有效回答查询。
-来自: [2025.acl-long.861_Shifting from Ranking to Set Selection for Retrieval Augmented Generation, 第4页, 2025.acl-long.861_Shifting from Ranking to Set Selection for Retrieval Augmented Generation_chunk_015]</t>
-  </si>
-  <si>
-    <t>Meta-Bench基准测试中，α参数的最优范围是多少？这个参数的作用是什么？</t>
-  </si>
-  <si>
     <t>α参数的最优范围在0.65到0.8之间。这个参数用于平衡工具描述和参数描述在工具检索中的权重。</t>
   </si>
   <si>
-    <t>在Meta-Tool中，α参数的最优范围是0.65到0.8。它的作用是平衡工具描述和参数描述在工具检索中的权重，以优化检索性能。
-来自: [2025.acl-long.1481_Meta-Tool, 第20页, 2025.acl-long.1481_Meta-Tool_chunk_071]</t>
-  </si>
-  <si>
     <t>CypherBench 是如何从 RDF 图生成领域特定属性图的？</t>
   </si>
   <si>
     <t>CypherBench 通过将 RDF 图转换为多个领域特定的属性图（domain-specific property graphs）来实现这一过程，并使用 Cypher 语言对其进行查询。</t>
   </si>
   <si>
-    <t>CypherBench 通过定义领域特定的模式（schema），并利用 RDF 到属性图的转换层，将 RDF 数据转换为多个领域特定的属性图视图。转换层负责数据类型转换和单位标准化，生成模式强制、严格类型化的数据；每个属性图视图包含所有符合其各自模式的数据。
-来自: [2025.acl-long.438_CypherBench, 第4页, 2025.acl-long.438_CypherBench_chunk_016][2025.acl-long.438_CypherBench, 第4页, 2025.acl-long.438_CypherBench_chunk_017]</t>
-  </si>
-  <si>
     <t xml:space="preserve"> ClinRaGen框架的三阶段理由蒸馏范式是什么？</t>
   </si>
   <si>
     <t>ClinRaGen框架采用三阶段理由蒸馏范式：第一阶段从医疗笔记中蒸馏理由，让SLM发展对文本临床信息的基础理解；第二阶段引入知识增强注意力，将数值实验室测试与结构化医学知识对齐，蒸馏实验室测试为基础的理由；第三阶段完全整合文本和数值输入，使SLM能够生成临床连贯的多模态理由以支持疾病诊断。</t>
-  </si>
-  <si>
-    <t>ClinRaGen的三阶段理由蒸馏范式为：第一阶段从医疗笔记中蒸馏理由，使小语言模型建立对文本临床信息的基础理解；第二阶段引入知识增强注意力，将数值实验室测试与结构化医学知识对齐，蒸馏基于实验室测试的理由；第三阶段完全整合文本和数值输入，使小语言模型生成临床连贯的多模态理由以支持疾病诊断。
-来自: [2025.acl-long.540_Knowledge-Augmented Multimodal Clinical Rationale Generation for Disease Diagnosis with Small Language Models, 第4页, 2025.acl-long.540_Knowledge-Augmented Multimodal Clinical Rationale Generation for Disease Diagnosis with Small Language Models_chunk_016]</t>
   </si>
   <si>
     <t>QAEncoder如何解决文档-查询差距问题？</t>
@@ -309,20 +221,12 @@
 文档指纹附加： 为这些嵌入表示附加文档指纹，以有效区分不同文档的嵌入，避免仅依赖查询期望导致的文档辨识度丢失问题。</t>
   </si>
   <si>
-    <t>QAEncoder通过为每个文档生成多样化的查询来创建语义对齐的嵌入，并采用文档指纹策略确保文档可区分性，从而弥合文档-查询差距。
-来自: [2025.acl-long.217_QAEncoder, 第5页, 2025.acl-long.217_QAEncoder_chunk_019]</t>
-  </si>
-  <si>
     <t>在 HALOGEN 的文本简化任务中，如何验证模型生成的简化文本是否忠实于原文？</t>
   </si>
   <si>
     <t>先用 GPT-3.5-turbo 将简化文本分解为独立的原子事实，再用 Llama-2-70B-chat 判断每个原子事实是否被原文蕴含。</t>
   </si>
   <si>
-    <t>在HALOGEN的文本简化任务中，验证模型生成简化文本忠实性的方法是：先使用GPT-3.5将简化文本分解为独立事实，然后使用Llama-2-70B判断每个原子事实是否由原文蕴含。
-来自: [2025.acl-long.71_HALoGEN, 第3页, 2025.acl-long.71_HALoGEN_chunk_017]</t>
-  </si>
-  <si>
     <t>在"CiteEval"论文中，GPT-4o和Llama-3-70B在Cited scenario和Full scenario下的表现有何差异？</t>
   </si>
   <si>
@@ -332,112 +236,64 @@
     <t>在Cited scenario下，GPT-4o表现最佳，Llama-3-70B与GPT-4o-mini相当；在Full scenario下，Llama-3-70B超越GPT-4o，取得最佳性能。</t>
   </si>
   <si>
-    <t>在Cited scenario下，GPT-4o是表现最好的模型，Llama-3-70B则与GPT-4o-mini水平相当；而在Full scenario下，Llama-3-70B的表现优于GPT-4o，取得了最佳性能。
-来自: [2025.acl-long.1574_CiteEval, 第8页, 2025.acl-long.1574_CiteEval_chunk_041]</t>
-  </si>
-  <si>
     <t>"FaithfulRAG"在FaithEval数据集上使用Mistral-7B作为backbone时的准确率是多少？相比最强基线提高了多少？</t>
   </si>
   <si>
     <t>81.7%，比最强基线(KRE的73.2%)提高了8.5%。</t>
   </si>
   <si>
-    <t>在FaithEval数据集上，以Mistral-7B为backbone的FaithfulRAG准确率为81.7%，相比最强基线（KRE的73.2%）提高了8.5%。
-来自: [2025.acl-long.1062_FaithfulRAG, 第7页, 2025.acl-long.1062_FaithfulRAG_chunk_037]</t>
-  </si>
-  <si>
     <t>RankCoT 相对于 vanilla RAG 模型的表现如何？这说明了什么？</t>
   </si>
   <si>
     <t>RankCoT 相比 vanilla RAG 模型有 2.5% 的提升，表明它在提供更有意义的细化方面有效，有助于 LLM 更好地回答问题。</t>
   </si>
   <si>
-    <t>RankCoT 在 Has-Answer 场景中优于所有知识精炼模型，在 Miss-Answer 场景中相比 vanilla RAG 表现出最显著的性能提升，在内部知识冲突场景中也优于 vanilla RAG。这说明 RankCoT 能有效整合查询相关信息、过滤噪声文档的误导、缓解知识冲突，并帮助 RAG 系统保持答案一致性。
-来自: [2025.acl-long.629_RankCoT, 第7页, 2025.acl-long.629_RankCoT_chunk_045] 和 [2025.acl-long.629_RankCoT, 第12页, 2025.acl-long.629_RankCoT_chunk_056]</t>
-  </si>
-  <si>
     <t>在 HALoGEN 基准测试中，表现最好的 LLM 生成事实的幻觉率范围是多少？</t>
   </si>
   <si>
     <t>实验发现，即使是表现最好的 LLM，其生成事实的幻觉率也在 3% 到 86% 之间，具体数值取决于所属领域。</t>
   </si>
   <si>
-    <t>在 HALoGEN 基准测试中，表现最好的 LLM 生成事实的幻觉率范围是 3% 到 86%，具体取决于任务领域。
-来自: [2025.acl-long.71_HALoGEN, 第1页, 2025.acl-long.71_HALoGEN_chunk_004]</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 在LongBench v2基准测试中，人类专家在15分钟时间限制下的准确率是多少？</t>
   </si>
   <si>
     <t>人类专家在15分钟时间限制下的准确率为53.7%。</t>
   </si>
   <si>
-    <t>人类专家在15分钟时间限制下的准确率为53.7%。
-来自: [2025.acl-long.183_LongBench v2, 第1页, 2025.acl-long.183_LongBench v2_chunk_001]</t>
-  </si>
-  <si>
     <t>AGENTSTAR方法在WebShop、ALFWorld和BabyAI任务上与GPT-4-Turbo相比有何优势？</t>
   </si>
   <si>
     <t>AGENTSTAR 在这三个任务上的性能全面超越了 GPT-4-Turbo。其中在 WebShop 上的提升最为显著（远超 GPT-4-Turbo 61 个百分点），在 ALFWorld 和 BabyAI 上也分别实现了大幅领先（超过 GPT-4-Turbo 20.5 和 9.87 个百分点）。</t>
   </si>
   <si>
-    <t>AGENTSTAR在WebShop、ALFWorld和BabyAI任务上的表现分别比GPT-4-Turbo高出61.00、20.50和9.87个点。
-来自: [2025.acl-long.1355_AgentGym, 第7页, 2025.acl-long.1355_AgentGym_chunk_045]</t>
-  </si>
-  <si>
     <t>在Humanity's Last Exam数据集上，Agentic Reasoning与DeepSeek-R1结合的性能提升是多少？与OpenAI Deep Research的差距如何变化？</t>
   </si>
   <si>
     <t>在Humanity's Last Exam数据集上，Agentic Reasoning与DeepSeek-R1结合达到了23.8%的准确率，比基础模型提升了14.4%，与专有的OpenAI Deep Research的差距缩小到仅2.8%。</t>
   </si>
   <si>
-    <t>在Humanity's Last Exam上，Agentic Reasoning结合DeepSeek-R1相比基础模型实现了14.4%的性能提升，与OpenAI Deep Research的差距缩小至仅2.8%。
-来自: [2025.acl-long.1383_Agentic Reasoning, 第1页, 2025.acl-long.1383_Agentic Reasoning_chunk_004]</t>
-  </si>
-  <si>
     <t>在GAIA基准测试中，Agentic Reasoning在不同级别任务上的表现如何？</t>
   </si>
   <si>
     <t>在GAIA基准测试中，Agentic Reasoning在Level 1和Level 2任务上超越了OpenAI的Deep Research，在Level 3任务上将差距缩小到2.26%。</t>
   </si>
   <si>
-    <t>在GAIA基准测试中，Agentic Reasoning在Level 1上达到74.36%，Level 2上达到69.21%，Level 3上达到45.46%，平均66.13%。它在所有公开方法中取得了最高水平，并在Level 1和Level 2上超越了OpenAI Deep Research，在Level 3上的差距缩小至2.26%。
-来自: [2025.acl-long.1383_Agentic Reasoning, 第5页, 2025.acl-long.1383_Agentic Reasoning_chunk_023]（具体分数）
-来自: [2025.acl-long.1383_Agentic Reasoning, 第5页, 2025.acl-long.1383_Agentic Reasoning_chunk_022]（与OpenAI Deep Research的比较）</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 在Asclepius医学基准测试中，人类医生与Med-MLLMs的表现对比如何？</t>
   </si>
   <si>
     <t>在Asclepius基准测试中，人类医生在所有专业领域都超过了Med-MLLMs。即使是平均准确率为57.4%的初级医生也略微超过了表现最好的Med-MLLM GPT-4V（准确率为54.3%）。这表明尽管人工智能取得了进步，但在诊断精度方面人类专业知识与当前Med-MLLMs之间仍存在差距。</t>
   </si>
   <si>
-    <t>人类医生在所有专科的诊断准确率上均超越Med-MLLMs，平均准确率在0.538至0.641之间，而所有Med-MLLMs的平均准确率均低于此范围。其中GPT-4V表现最接近人类医生，准确率为54.3%，但仍低于初级医生的57.4%。此外，Med-MLLMs在不同专科间的表现变异性明显低于人类医生。
-来自: [2025.acl-long.1178_Asclepius, 第7页, 2025.acl-long.1178_Asclepius_chunk_032]
-来自: [2025.acl-long.1178_Asclepius, 第15页, 2025.acl-long.1178_Asclepius_chunk_048]
-来自: [2025.acl-long.1178_Asclepius, 第7页, 2025.acl-long.1178_Asclepius_chunk_029]</t>
-  </si>
-  <si>
     <t>在LongDocURL基准测试中，GPT-4o的表现如何？其他开源模型呢？</t>
   </si>
   <si>
     <t>在LongDocURL基准测试中，只有GPT-4o达到了及格标准，得分为64.5，表明该基准对当前模型提出了重大挑战。在开源模型中，只有Qwen2-VL（得分30.6）和LLaVA-OneVision（得分22.0和25.0）超过了20分的阈值，其他参数少于13B的模型都低于这个阈值。</t>
   </si>
   <si>
-    <t>在LongDocURL基准测试中，GPT-4o取得了64.5的最高分，是唯一达到及格标准的模型。开源模型表现明显较弱，最好的开源模型Qwen2-VL仅得30.6分，LLaVA-OneVision分别得到22.0和25.0分，其余开源模型得分均低于20。
-来自: [2025.acl-long.57_LongDocURL, 第2页, 2025.acl-long.57_LongDocURL_chunk_007]
-来自: [2025.acl-long.57_LongDocURL, 第6页, 2025.acl-long.57_LongDocURL_chunk_026]</t>
-  </si>
-  <si>
     <t>RAGEval 提出的自动评估指标与人工评估的一致性如何？</t>
   </si>
   <si>
     <t>实验结果表明，RAGEval 的机器自动评估与人工评估在所有指标上均表现出高度一致性。两者之间的最终绝对差异仅为 1.67%。</t>
-  </si>
-  <si>
-    <t>RAGEval 使用 LLM 对提出的指标进行评分，与人工评估表现出高度一致性。
-来自: [2025.acl-long.418_RAGEval, 第1页, 2025.acl-long.418_RAGEval_chunk_001]</t>
   </si>
   <si>
     <t>在利用大模型内部知识应对知识冲突时，《Astute RAG》与《FaithfulRAG》各自采用了什么核心机制/模块来提取或生成内部知识？</t>
@@ -450,30 +306,16 @@
 《FaithfulRAG》：采用自我事实挖掘 模块，通过外部化大模型对问题的理解，提取出细粒度的、事实级别的内部知识。</t>
   </si>
   <si>
-    <t>《Astute RAG》采用自适应引出（adaptively elicits）机制来提取大模型内部知识；《FaithfulRAG》则通过 Self-Fact Mining 模块将模型的参数化知识具体化为事实层面的内部知识。
-来自: [2025.acl-long.1476_Astute RAG, 第1页, 2025.acl-long.1476_Astute RAG_chunk_001] 和 [2025.acl-long.1062_FaithfulRAG, 第9页, 2025.acl-long.1062_FaithfulRAG_chunk_050]</t>
-  </si>
-  <si>
     <t>"UniRAG"和"FaithfulRAG"在处理查询理解方面的核心创新分别是什么？</t>
   </si>
   <si>
     <t>UniRAG提出统一的查询理解框架，集成查询增强和查询编码两个阶段；FaithfulRAG通过自我事实挖掘和自思考模块，在事实级别识别并解决参数化知识与检索上下文之间的冲突，提高语义一致性。</t>
   </si>
   <si>
-    <t>UniRAG 的核心创新在于构建统一的查询理解框架，将查询增强与编码集成到单一模型中，通过自适应选择增强策略和对比学习来提升查询理解和检索准确性。FaithfulRAG 的核心创新则聚焦于从查询中挖掘模型自身的参数知识（Self‑Fact Mining），将其具体化为事实并与检索上下文对齐，进而在事实层面识别和解决知识冲突，从而深化对查询的语义理解。
-来自: [2025.acl-long.693_UniRAG, 第9页, 2025.acl-long.693_UniRAG_chunk_042]
-来自: [2025.acl-long.1062_FaithfulRAG, 第4页, 2025.acl-long.1062_FaithfulRAG_chunk_015]
-来自: [2025.acl-long.1062_FaithfulRAG, 第9页, 2025.acl-long.1062_FaithfulRAG_chunk_050]</t>
-  </si>
-  <si>
     <t>比较MEMERAG和DragonBall两个基准的异同点，它们各自关注的评估维度是什么？</t>
   </si>
   <si>
     <t>相同点：两者都是多语言RAG评估基准。不同点：MEMERAG专注于多语言端到端元评估，使用母语问题并由专家评估忠实度和相关性；DragonBall是一个多场景多语言RAG全能基准，涵盖金融、法律、医疗领域，包含6,711个问题，用于评估RAG系统在不同场景下的性能。</t>
-  </si>
-  <si>
-    <t>MEMERAG和DragonBall都是面向RAG系统的多语言基准，但评估维度不同。MEMERAG聚焦于生成内容的评估，通过人类专家对每个生成句子标注忠实度（faithfulness）和相关性（relevance），形成一个元评估基准，用于衡量自动评估器与人类判断的相关性。DragonBall则聚焦于检索阶段的性能，主要评估召回率（Recall）和EIR等检索指标。两者的共同点在于都支持多语言场景：MEMERAG覆盖5种语言，DragonBall包含中英文数据。
-来自: [2025.acl-long.1101_MEMERAG, 第3页, 2025.acl-long.1101_MEMERAG_chunk_014]；[2025.acl-long.418_RAGEval, 第4页, 2025.acl-long.418_RAGEval_chunk_018]；[2025.acl-long.418_RAGEval, 第17页, 2025.acl-long.418_RAGEval_chunk_064]</t>
   </si>
   <si>
     <t>SYNQA 和 RHIO 分别通过什么方式生成训练数据？这两种数据生成策略在提升模型归因能力上有什么不同？</t>
@@ -493,11 +335,6 @@
 AGENTGYM：专注于代理训练和工具使用的环境集合，包含11个不同的交互环境（如Minecraft、ScienceWorld、BabyAI等），用于训练和评估LLM代理在多样化任务中的能力</t>
   </si>
   <si>
-    <t>LongBench v2 是一个静态的基准测试，用于评估大语言模型在长上下文（8k–2M词）下的深度理解与推理能力，覆盖单文档问答、多文档问答等真实场景。AGENTGYM 则是一个交互式框架，提供14种环境，支持对通用大语言模型代理进行训练和评估，强调多环境下的交互探索与学习。
-来自: [2025.acl-long.183_LongBench v2, 第1页, 2025.acl-long.183_LongBench v2_chunk_001]  
-来自: [2025.acl-long.1355_AgentGym, 第1页, 2025.acl-long.1355_AgentGym_chunk_004]</t>
-  </si>
-  <si>
     <t>Agentic Reasoning 与 AR-MCTS 分别采用什么核心机制来提升复杂推理能力？</t>
   </si>
   <si>
@@ -505,25 +342,11 @@
 AR-MCTS：基于蒙特卡洛树搜索（MCTS），在扩展阶段集成主动检索（Active Retrieval） 机制，自动获取逐步推理的高质量标注，渐进式提升多模态大模型的推理能力。</t>
   </si>
   <si>
-    <t>Agentic Reasoning 的核心机制是将外部基于 LLM 的智能体（Agent）作为工具集成到推理过程中，通过委托 Web-Search、Code 和 Mind-Map 等辅助智能体来增强问题解决能力。  
-AR-MCTS 的核心机制是将主动检索（Active Retrieval）与蒙特卡洛树搜索（MCTS）相结合，自动获取高质量的逐步推理标注，并逐步对齐过程奖励模型（PRM）以实现过程级的多模态推理验证。
-来自: [2025.acl-long.1383_Agentic Reasoning, 第2页, 2025.acl-long.1383_Agentic Reasoning_chunk_008]  
-来自: [2025.acl-long.180_Progressive Multimodal Reasoning via Active Retrieval, 第1页, 2025.acl-long.180_Progressive Multimodal Reasoning via Active Retrieval_chunk_000]  
-来自: [2025.acl-long.180_Progressive Multimodal Reasoning via Active Retrieval, 第9页, 2025.acl-long.180_Progressive Multimodal Reasoning via Active Retrieval_chunk_047]</t>
-  </si>
-  <si>
     <t>MAIN‑RAG 与 RAG‑Critic 在提升 RAG 系统可靠性方面分别采用了什么核心方法？</t>
   </si>
   <si>
     <t>MAIN‑RAG 采用多智能体协作过滤机制，通过三个 LLM 智能体（Predictor、Judge、Final‑Predictor）对检索文档进行相关性评分和排序，并利用自适应阈值动态过滤噪声文档，无需训练。
 RAG‑Critic 采用批评引导的智能体工作流，首先构建层次化 RAG 错误系统（3 级错误类型，含 4000+ 细粒度标签），然后训练轻量级错误批评模型进行自动错误诊断，最后通过规划智能体根据错误反馈定制并执行修正方案。</t>
-  </si>
-  <si>
-    <t>MAIN‑RAG 采用训练无关的多智能体协同过滤方法，通过多个 LLM 智能体对检索文档进行评分与过滤，并自适应调整相关性阈值，以共识驱动策略筛选高质量文档来提升可靠性。  
-RAG‑Critic 采用批评引导的智能体工作流方法，先构建层次化 RAG 错误系统并训练错误批评模型，再根据细粒度错误反馈自动定制纠正方案，实现错误驱动的自主修正来提升可靠性。
-来自: [2025.acl-long.131_MAIN-RAG, 第1页, 2025.acl-long.131_MAIN-RAG_chunk_006]  
-来自: [2025.acl-long.179_RAG-Critic, 第8页, 2025.acl-long.179_RAG-Critic_chunk_040]  
-来自: [2025.acl-long.179_RAG-Critic, 第9页, 2025.acl-long.179_RAG-Critic_chunk_047]</t>
   </si>
   <si>
     <t>在构建可靠的问答（QA）系统时，这QAEncoder与On Synthesizing Data for Context Attribution in Question Answering两篇论文分别侧重于优化系统工作流的哪个阶段？它们各自试图解决的核心痛点是什么？</t>
@@ -535,62 +358,385 @@
 核心痛点：大语言模型在生成答案时容易产生幻觉，用户很难验证生成的答案是否真的基于提供的上下文，缺乏可解释性和事实依据。</t>
   </si>
   <si>
+    <t>这10篇论文中哪一篇提出了名为"RAG-Guard"的安全防护框架？</t>
+  </si>
+  <si>
+    <t>不可回答类</t>
+  </si>
+  <si>
+    <t>无法回答。</t>
+  </si>
+  <si>
+    <t>"ProLong"模型在训练过程中使用了哪种具体的优化器来处理长序列训练的梯度问题？</t>
+  </si>
+  <si>
+    <t>SETR模型在训练时具体的训练时间是多少小时？</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> L-CiteEval基准中使用的NLI模型deberta-base-long-nli的准确率是多少？该模型在哪些具体数据集上进行了训练？</t>
+  </si>
+  <si>
+    <t>论文中是否提到了SYNQA方法在医疗领域的具体应用案例？</t>
+  </si>
+  <si>
+    <t>论文中是否提供了RHIO方法在实时应用场景中的延迟测试数据？</t>
+  </si>
+  <si>
+    <t>Agentic Reasoning框架中使用的Mind-Map agent的具体神经网络架构是什么？</t>
+  </si>
+  <si>
+    <t>在CypherBench基准测试中，每个问题模板具体包含多少个训练样本？</t>
+  </si>
+  <si>
+    <t>【总体平均值】</t>
+  </si>
+  <si>
+    <t>【定义类平均值】</t>
+  </si>
+  <si>
+    <t>【方法细节类平均值】</t>
+  </si>
+  <si>
+    <t>【实验结果类平均值】</t>
+  </si>
+  <si>
+    <t>【跨论文比较类平均值】</t>
+  </si>
+  <si>
+    <t>【不可回答类平均值】</t>
+  </si>
+  <si>
+    <t>question</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>作者将post-training scaling分为三个主要方法：监督微调（Supervised Fine-tuning, SFT）、强化学习（Reinforcement Learning, RL）和测试时计算（Test-time Compute, TTC）。
+来自: [A Survey of Post-Training Scaling in Large Language Models, 第2页, A Survey of Post-Training Scaling in Large Language Models_chunk_008]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在Humanity's Last Exam上，Agentic Reasoning结合DeepSeek-R1相比基础模型实现了14.4%的性能提升，与OpenAI Deep Research的差距缩小至仅2.8%。
+来自: [Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools, 第1页, Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools_chunk_004]</t>
+  </si>
+  <si>
+    <t>在GAIA基准测试中，Agentic Reasoning在Level 1上达到74.36%，Level 2上达到69.21%，Level 3上达到45.46%，平均66.13%。它在所有公开方法中取得了最高水平，并在Level 1和Level 2上超越了OpenAI Deep Research，在Level 3上的差距缩小至2.26%。
+来自: [Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools, 第5页, Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools_chunk_023]（具体分数）
+来自: [Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools, 第5页, Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools_chunk_022]（与OpenAI Deep Research的比较）</t>
+  </si>
+  <si>
+    <t>知识整合过程包含三个主要步骤：合并一致信息、识别冲突信息、过滤无关信息。
+来自: [ASTUTE RAG: Overcoming Imperfect Retrieval Augmentation and Knowledge Conflicts for Large Language Models, 第2页, ASTUTE RAG: Overcoming Imperfect Retrieval Augmentation and Knowledge Conflicts for Large Language Models_chunk_007] 和 [ASTUTE RAG: Overcoming Imperfect Retrieval Augmentation and Knowledge Conflicts for Large Language Models, 第16页, ASTUTE RAG: Overcoming Imperfect Retrieval Augmentation and Knowledge Conflicts for Large Language Models_chunk_046]</t>
+  </si>
+  <si>
+    <r>
+      <t>Meta-Bench基准测试中，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>α</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>参数的最优范围是多少？这个参数的作用是什么？</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>QAEncoder 侧重于优化检索阶段，其核心痛点是文档与查询之间的语义差距（document-query gap），即用户查询与待检索文档在词汇、句法、语义等维度上的不匹配问题。  
 On Synthesizing Data for Context Attribution in Question Answering 则侧重于生成后的归因阶段，其核心痛点是上下文归因（context attribution）问题，即如何让模型在给出答案的同时，准确指出答案所依据的支持性句子或证据。
-来自: [2025.acl-long.217_QAEncoder, 第2页, 2025.acl-long.217_QAEncoder_chunk_007]  
-来自: [2025.acl-long.217_QAEncoder, 第1页, 2025.acl-long.217_QAEncoder_chunk_002]  
-来自: [2025.acl-long.828_On Synthesizing Data for Context Attribution in Question Answering, 第17页, 2025.acl-long.828_On Synthesizing Data for Context Attribution in Question Answering_chunk_071]</t>
-  </si>
-  <si>
-    <t>这10篇论文中哪一篇提出了名为"RAG-Guard"的安全防护框架？</t>
-  </si>
-  <si>
-    <t>不可回答类</t>
-  </si>
-  <si>
-    <t>无法回答。</t>
-  </si>
-  <si>
-    <t>"ProLong"模型在训练过程中使用了哪种具体的优化器来处理长序列训练的梯度问题？</t>
-  </si>
-  <si>
-    <t>SETR模型在训练时具体的训练时间是多少小时？</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> L-CiteEval基准中使用的NLI模型deberta-base-long-nli的准确率是多少？该模型在哪些具体数据集上进行了训练？</t>
-  </si>
-  <si>
-    <t>论文中是否提到了SYNQA方法在医疗领域的具体应用案例？</t>
-  </si>
-  <si>
-    <t>论文中是否提供了RHIO方法在实时应用场景中的延迟测试数据？</t>
-  </si>
-  <si>
-    <t>Agentic Reasoning框架中使用的Mind-Map agent的具体神经网络架构是什么？</t>
-  </si>
-  <si>
-    <t>在CypherBench基准测试中，每个问题模板具体包含多少个训练样本？</t>
-  </si>
-  <si>
-    <t>【总体平均值】</t>
-  </si>
-  <si>
-    <t>【定义类平均值】</t>
-  </si>
-  <si>
-    <t>【方法细节类平均值】</t>
-  </si>
-  <si>
-    <t>【实验结果类平均值】</t>
-  </si>
-  <si>
-    <t>【跨论文比较类平均值】</t>
-  </si>
-  <si>
-    <t>【不可回答类平均值】</t>
-  </si>
-  <si>
-    <t>question</t>
+来自: [QAEncoder: Towards Aligned Representation Learning in Question Answering Systems, 第2页, QAEncoder: Towards Aligned Representation Learning in Question Answering Systems_chunk_007]  
+来自: [QAEncoder: Towards Aligned Representation Learning in Question Answering Systems, 第1页, QAEncoder: Towards Aligned Representation Learning in Question Answering Systems_chunk_002]  
+来自: [On Synthesizing Data for Context Attribution in Question Answering, 第17页, On Synthesizing Data for Context Attribution in Question Answering_chunk_071]</t>
+  </si>
+  <si>
+    <t>在 HALoGEN 基准测试中，表现最好的 LLM 生成事实的幻觉率范围是 3% 到 86%，具体取决于任务领域。
+来自: [HALOGEN :FantasticLLMHallucinations and Where to Find Them, 第1页, HALOGEN :FantasticLLMHallucinations and Where to Find Them_chunk_004]</t>
+  </si>
+  <si>
+    <t>《Astute RAG》采用自适应引出（adaptively elicits）机制来提取大模型内部知识；《FaithfulRAG》则通过 Self-Fact Mining 模块将模型的参数化知识具体化为事实层面的内部知识。
+来自: [ASTUTE RAG: Overcoming Imperfect Retrieval Augmentation and Knowledge Conflicts for Large Language Models, 第1页, ASTUTE RAG: Overcoming Imperfect Retrieval Augmentation and Knowledge Conflicts for Large Language Models_chunk_001] 和 [FaithfulRAG: Fact-Level Conflict Modeling for Context-Faithful Retrieval-Augmented Generation, 第9页, FaithfulRAG: Fact-Level Conflict Modeling for Context-Faithful Retrieval-Augmented Generation_chunk_050]</t>
+  </si>
+  <si>
+    <t>LongBench v2 是一个静态的基准测试，用于评估大语言模型在长上下文（8k–2M词）下的深度理解与推理能力，覆盖单文档问答、多文档问答等真实场景。AGENTGYM 则是一个交互式框架，提供14种环境，支持对通用大语言模型代理进行训练和评估，强调多环境下的交互探索与学习。
+来自: [LongBench v2: Towards Deeper Understanding and Reasoning on Realistic Long-context Multitasks, 第1页, LongBench v2: Towards Deeper Understanding and Reasoning on Realistic Long-context Multitasks_chunk_001]  
+来自: [AGENTGYM: Evaluating and Training Large Language Model-based Agents across Diverse Environments, 第1页, AGENTGYM: Evaluating and Training Large Language Model-based Agents across Diverse Environments_chunk_004]</t>
+  </si>
+  <si>
+    <t>Silver noise是指部分包含答案的证据。
+来自: [SafeRAG: Benchmarking Security in Retrieval-Augmented Generation of Large Language Model, 第2页, SafeRAG: Benchmarking Security in Retrieval-Augmented Generation of Large Language Model_chunk_007]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAG噪声被分为有益噪声和有害噪声两类。
+来自: [Pandora’s Box or Aladdin’s Lamp: A Comprehensive Analysis Revealing the Role of RAG Noise in Large Language Models, 第2页, Pandora’s Box or Aladdin’s Lamp: A Comprehensive Analysis Revealing the Role of RAG Noise in Large Language Models_chunk_006]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ref-Long是一个专门设计用于评估长上下文语言模型的长上下文引用能力的基准。
+来自: [Ref-Long: Benchmarking the Long-context Referencing Capability of Long-context Language Models, 第1页, Ref-Long: Benchmarking the Long-context Referencing Capability of Long-context Language Models_chunk_001]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SYNQA是一种生成式方法，给定选定的上下文句子，由大语言模型生成完全由这些句子支持的问答对。
+来自: [On Synthesizing Data for Context Attribution in Question Answering, 第2页, On Synthesizing Data for Context Attribution in Question Answering_chunk_009]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AgenticLU是一个通过将目标自澄清与上下文接地整合到智能体工作流中来增强大语言模型对长上下文查询理解的框架。
+来自: [Self-Taught Agentic Long-Context Understanding, 第1页, Self-Taught Agentic Long-Context Understanding_chunk_001]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Agentic Reasoning 是一个通过将外部基于LLM的智能体作为工具集成到推理过程中，从而增强大语言模型推理能力的框架。
+来自: [Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools, 第2页, Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools_chunk_008]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>REAL-MM-RAG 基准测试旨在解决的四个关键属性是：(i) 多模态文档（包含文本、图表、表格等视觉元素）；(ii) 增强难度（需要超越简单关键词匹配，在上下文相似的页面中进行挑战性评估）；(iii) 真实 RAG 查询（问题自然提出，不显式引用页面，反映真实检索场景）；(iv) 准确标注（所有相关文档必须被正确且穷尽地标注，以避免低估检索性能并防止假阴性）。
+来自: [REAL-MM-RAG:AReal-World Multi-Modal Retrieval Benchmark, 第1页, REAL-MM-RAG:AReal-World Multi-Modal Retrieval Benchmark_chunk_003]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ASTUTE RAG是一种新颖的检索增强生成方法，旨在对不完美的检索增强具有鲁棒性，同时保留可靠检索时的 grounding 效果。它用于缓解不完美检索增强的影响，解决LLM内部知识与外部知识之间的冲突，从而生成更准确可靠的响应。
+来自: [ASTUTE RAG: Overcoming Imperfect Retrieval Augmentation and Knowledge Conflicts for Large Language Models, 第2页, ASTUTE RAG: Overcoming Imperfect Retrieval Augmentation and Knowledge Conflicts for Large Language Models_chunk_007] 和 [ASTUTE RAG: Overcoming Imperfect Retrieval Augmentation and Knowledge Conflicts for Large Language Models, 第4页, ASTUTE RAG: Overcoming Imperfect Retrieval Augmentation and Knowledge Conflicts for Large Language Models_chunk_016]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>L-CiteEval是一个开箱即用的评估套件，包含多任务长上下文基准和相应的评估流程。
+来自: [L-CiteEval: A Suite for Evaluating Fidelity of Long-context Models, 第8页, L-CiteEval: A Suite for Evaluating Fidelity of Long-context Models_chunk_056]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LongBench v2 包含 503 个多项选择题，上下文长度范围从 8k 到 2M 词。
+来自: [LongBench v2: Towards Deeper Understanding and Reasoning on Realistic Long-context Multitasks, 第1页, LongBench v2: Towards Deeper Understanding and Reasoning on Realistic Long-context Multitasks_chunk_004]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RHIO框架的三个主要组成部分是：不忠实数据增强（unfaithful data augmentation）、忠实性感知调优（faithfulness-aware tuning）和自诱导解码（self-induced decoding）。
+来自: [Improving Contextual Faithfulness of Large Language Models via Retrieval Heads-Induced Optimization, 第15页, Improving Contextual Faithfulness of Large Language Models via Retrieval Heads-Induced Optimization_chunk_065]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>作者发现使用标准的短上下文指令数据集（如Ultra-Chat）就足以在长上下文任务上取得良好性能，而长合成指令数据不会进一步提升性能。
+来自: [How to Train Long-Context Language Models (Effectively), 第2页, How to Train Long-Context Language Models (Effectively)_chunk_006]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LongRefiner 将推理过程拆分为离线和在线两个阶段：离线阶段预先对语料库中的文档执行层次化结构处理，在线阶段仅需对用户查询进行分析并完成自适应精炼，从而大幅减少在线处理的输入和输出 token 数量，使整体延迟降至标准设置的约 25%。
+来自: [Hierarchical Document Refinement for Long-context Retrieval-augmented Generation, 第6页, Hierarchical Document Refinement for Long-context Retrieval-augmented Generation_chunk_030]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DRAG框架通过本地模型在将查询上传到云端之前重新表述或剥离敏感信息，确保隐私数据不离开本地；云端模型仅处理清理后的查询并返回证据和知识图谱，本地模型再生成最终答案。
+来自: [DRAG: Distilling RAG for SLMs from LLMs to Transfer Knowledge and Mitigate Hallucination via Evidence and Graph-based Distillation, 第1页, DRAG: Distilling RAG for SLMs from LLMs to Transfer Knowledge and Mitigate Hallucination via Evidence and Graph-based Distillation_chunk_004]
+来自: [DRAG: Distilling RAG for SLMs from LLMs to Transfer Knowledge and Mitigate Hallucination via Evidence and Graph-based Distillation, 第5页, DRAG: Distilling RAG for SLMs from LLMs to Transfer Knowledge and Mitigate Hallucination via Evidence and Graph-based Distillation_chunk_025]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SG-MCTS 在每次迭代中依次执行四个步骤：选择（selection）、反思引导的扩展（reflection-guided expansion）、评估（evaluation）和反向传播（backpropagation）。
+来自: [Think&amp;Cite: Improving Attributed Text Generation with Self-Guided Tree Search and Progress Reward Modeling, 第3页, Think&amp;Cite: Improving Attributed Text Generation with Self-Guided Tree Search and Progress Reward Modeling_chunk_014]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SETR 的段落选择提示引导的三个关键步骤是：(1) 列举回答查询所需的关键信息需求；(2) 为每个需求识别包含相关信息的段落；(3) 选择一组段落，这些段落共同提供最全面和多样化的覆盖，以有效回答查询。
+来自: [Shifting from Ranking to Set Selection for Retrieval Augmented Generation, 第4页, Shifting from Ranking to Set Selection for Retrieval Augmented Generation_chunk_015]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>在Meta-Tool中，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>α</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>参数的最优范围是0.65到0.8。它的作用是平衡工具描述和参数描述在工具检索中的权重，以优化检索性能。
+来自: [Meta-Tool: Unleash Open-World Function Calling Capabilities of General-Purpose Large Language Models, 第20页, Meta-Tool: Unleash Open-World Function Calling Capabilities of General-Purpose Large Language Models_chunk_071]</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CypherBench 通过定义领域特定的模式（schema），并利用 RDF 到属性图的转换层，将 RDF 数据转换为多个领域特定的属性图视图。转换层负责数据类型转换和单位标准化，生成模式强制、严格类型化的数据；每个属性图视图包含所有符合其各自模式的数据。
+来自: [CYPHERBENCH: Towards Precise Retrieval over Full-scale Modern Knowledge Graphs in the LLM Era, 第4页, CYPHERBENCH: Towards Precise Retrieval over Full-scale Modern Knowledge Graphs in the LLM Era_chunk_016][CYPHERBENCH: Towards Precise Retrieval over Full-scale Modern Knowledge Graphs in the LLM Era, 第4页, CYPHERBENCH: Towards Precise Retrieval over Full-scale Modern Knowledge Graphs in the LLM Era_chunk_017]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClinRaGen的三阶段理由蒸馏范式为：第一阶段从医疗笔记中蒸馏理由，使小语言模型建立对文本临床信息的基础理解；第二阶段引入知识增强注意力，将数值实验室测试与结构化医学知识对齐，蒸馏基于实验室测试的理由；第三阶段完全整合文本和数值输入，使小语言模型生成临床连贯的多模态理由以支持疾病诊断。
+来自: [Knowledge-Augmented Multimodal Clinical Rationale Generation for Disease Diagnosis with Small Language Models, 第4页, Knowledge-Augmented Multimodal Clinical Rationale Generation for Disease Diagnosis with Small Language Models_chunk_016]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>QAEncoder通过为每个文档生成多样化的查询来创建语义对齐的嵌入，并采用文档指纹策略确保文档可区分性，从而弥合文档-查询差距。
+来自: [QAEncoder: Towards Aligned Representation Learning in Question Answering Systems, 第5页, QAEncoder: Towards Aligned Representation Learning in Question Answering Systems_chunk_019]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在HALOGEN的文本简化任务中，验证模型生成简化文本忠实性的方法是：先使用GPT-3.5将简化文本分解为独立事实，然后使用Llama-2-70B判断每个原子事实是否由原文蕴含。
+来自: [HALOGEN :FantasticLLMHallucinations and Where to Find Them, 第3页, HALOGEN :FantasticLLMHallucinations and Where to Find Them_chunk_017]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在Cited scenario下，GPT-4o是表现最好的模型，Llama-3-70B则与GPT-4o-mini水平相当；而在Full scenario下，Llama-3-70B的表现优于GPT-4o，取得了最佳性能。
+来自: [CiteEval: Principle-Driven Citation Evaluation for Source Attribution, 第8页, CiteEval: Principle-Driven Citation Evaluation for Source Attribution_chunk_041]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在FaithEval数据集上，以Mistral-7B为backbone的FaithfulRAG准确率为81.7%，相比最强基线（KRE的73.2%）提高了8.5%。
+来自: [FaithfulRAG: Fact-Level Conflict Modeling for Context-Faithful Retrieval-Augmented Generation, 第7页, FaithfulRAG: Fact-Level Conflict Modeling for Context-Faithful Retrieval-Augmented Generation_chunk_037]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RankCoT 在 Has-Answer 场景中优于所有知识精炼模型，在 Miss-Answer 场景中相比 vanilla RAG 表现出最显著的性能提升，在内部知识冲突场景中也优于 vanilla RAG。这说明 RankCoT 能有效整合查询相关信息、过滤噪声文档的误导、缓解知识冲突，并帮助 RAG 系统保持答案一致性。
+来自: [RankCoT: Refining Knowledge for Retrieval-Augmented Generation through Ranking Chain-of-Thoughts, 第7页, RankCoT: Refining Knowledge for Retrieval-Augmented Generation through Ranking Chain-of-Thoughts_chunk_045] 和 [RankCoT: Refining Knowledge for Retrieval-Augmented Generation through Ranking Chain-of-Thoughts, 第12页, RankCoT: Refining Knowledge for Retrieval-Augmented Generation through Ranking Chain-of-Thoughts_chunk_056]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGENTSTAR在WebShop、ALFWorld和BabyAI任务上的表现分别比GPT-4-Turbo高出61.00、20.50和9.87个点。
+来自: [AGENTGYM: Evaluating and Training Large Language Model-based Agents across Diverse Environments, 第7页, AGENTGYM: Evaluating and Training Large Language Model-based Agents across Diverse Environments_chunk_045]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人类医生在所有专科的诊断准确率上均超越Med-MLLMs，平均准确率在0.538至0.641之间，而所有Med-MLLMs的平均准确率均低于此范围。其中GPT-4V表现最接近人类医生，准确率为54.3%，但仍低于初级医生的57.4%。此外，Med-MLLMs在不同专科间的表现变异性明显低于人类医生。
+来自: [Asclepius: A Spectrum Evaluation Benchmark for Medical Multi-Modal Large Language Models, 第7页, Asclepius: A Spectrum Evaluation Benchmark for Medical Multi-Modal Large Language Models_chunk_032]
+来自: [Asclepius: A Spectrum Evaluation Benchmark for Medical Multi-Modal Large Language Models, 第15页, Asclepius: A Spectrum Evaluation Benchmark for Medical Multi-Modal Large Language Models_chunk_048]
+来自: [Asclepius: A Spectrum Evaluation Benchmark for Medical Multi-Modal Large Language Models, 第7页, Asclepius: A Spectrum Evaluation Benchmark for Medical Multi-Modal Large Language Models_chunk_029]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在LongDocURL基准测试中，GPT-4o取得了64.5的最高分，是唯一达到及格标准的模型。开源模型表现明显较弱，最好的开源模型Qwen2-VL仅得30.6分，LLaVA-OneVision分别得到22.0和25.0分，其余开源模型得分均低于20。
+来自: [LongDocURL: a Comprehensive Multimodal Long Document Benchmark Integrating Understanding, Reasoning, and Locating, 第2页, LongDocURL: a Comprehensive Multimodal Long Document Benchmark Integrating Understanding, Reasoning, and Locating_chunk_007]
+来自: [LongDocURL: a Comprehensive Multimodal Long Document Benchmark Integrating Understanding, Reasoning, and Locating, 第6页, LongDocURL: a Comprehensive Multimodal Long Document Benchmark Integrating Understanding, Reasoning, and Locating_chunk_026]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAGEval 使用 LLM 对提出的指标进行评分，与人工评估表现出高度一致性。
+来自: [RAGEval: Scenario Specific RAG Evaluation Dataset Generation Framework, 第1页, RAGEval: Scenario Specific RAG Evaluation Dataset Generation Framework_chunk_001]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>UniRAG 的核心创新在于构建统一的查询理解框架，将查询增强与编码集成到单一模型中，通过自适应选择增强策略和对比学习来提升查询理解和检索准确性。FaithfulRAG 的核心创新则聚焦于从查询中挖掘模型自身的参数知识（Self</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Fact Mining），将其具体化为事实并与检索上下文对齐，进而在事实层面识别和解决知识冲突，从而深化对查询的语义理解。
+来自: [UniRAG: Unified Query Understanding Method for Retrieval Augmented Generation, 第9页, UniRAG: Unified Query Understanding Method for Retrieval Augmented Generation_chunk_042]
+来自: [FaithfulRAG: Fact-Level Conflict Modeling for Context-Faithful Retrieval-Augmented Generation, 第4页, FaithfulRAG: Fact-Level Conflict Modeling for Context-Faithful Retrieval-Augmented Generation_chunk_015]
+来自: [FaithfulRAG: Fact-Level Conflict Modeling for Context-Faithful Retrieval-Augmented Generation, 第9页, FaithfulRAG: Fact-Level Conflict Modeling for Context-Faithful Retrieval-Augmented Generation_chunk_050]</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MEMERAG和DragonBall都是面向RAG系统的多语言基准，但评估维度不同。MEMERAG聚焦于生成内容的评估，通过人类专家对每个生成句子标注忠实度（faithfulness）和相关性（relevance），形成一个元评估基准，用于衡量自动评估器与人类判断的相关性。DragonBall则聚焦于检索阶段的性能，主要评估召回率（Recall）和EIR等检索指标。两者的共同点在于都支持多语言场景：MEMERAG覆盖5种语言，DragonBall包含中英文数据。
+来自: [MEMERAG:AMultilingual End-to-End Meta-Evaluation Benchmark for Retrieval Augmented Generation, 第3页, MEMERAG:AMultilingual End-to-End Meta-Evaluation Benchmark for Retrieval Augmented Generation_chunk_014]；[RAGEval: Scenario Specific RAG Evaluation Dataset Generation Framework, 第4页, RAGEval: Scenario Specific RAG Evaluation Dataset Generation Framework_chunk_018]；[RAGEval: Scenario Specific RAG Evaluation Dataset Generation Framework, 第17页, RAGEval: Scenario Specific RAG Evaluation Dataset Generation Framework_chunk_064]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Agentic Reasoning 的核心机制是将外部基于 LLM 的智能体（Agent）作为工具集成到推理过程中，通过委托 Web-Search、Code 和 Mind-Map 等辅助智能体来增强问题解决能力。  
+AR-MCTS 的核心机制是将主动检索（Active Retrieval）与蒙特卡洛树搜索（MCTS）相结合，自动获取高质量的逐步推理标注，并逐步对齐过程奖励模型（PRM）以实现过程级的多模态推理验证。
+来自: [Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools, 第2页, Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools_chunk_008]  
+来自: [Progressive Multimodal Reasoning via Active Retrieval, 第1页, Progressive Multimodal Reasoning via Active Retrieval_chunk_000]  
+来自: [Progressive Multimodal Reasoning via Active Retrieval, 第9页, Progressive Multimodal Reasoning via Active Retrieval_chunk_047]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>MAIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RAG 采用训练无关的多智能体协同过滤方法，通过多个 LLM 智能体对检索文档进行评分与过滤，并自适应调整相关性阈值，以共识驱动策略筛选高质量文档来提升可靠性。  
+RAG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Critic 采用批评引导的智能体工作流方法，先构建层次化 RAG 错误系统并训练错误批评模型，再根据细粒度错误反馈自动定制纠正方案，实现错误驱动的自主修正来提升可靠性。
+来自: [MAIN-RAG: Multi-Agent Filtering Retrieval-Augmented Generation, 第1页, MAIN-RAG: Multi-Agent Filtering Retrieval-Augmented Generation_chunk_006]  
+来自: [RAG-Critic: Leveraging Automated Critic-Guided Agentic Workflow for Retrieval Augmented Generation, 第8页, RAG-Critic: Leveraging Automated Critic-Guided Agentic Workflow for Retrieval Augmented Generation_chunk_040]  
+来自: [RAG-Critic: Leveraging Automated Critic-Guided Agentic Workflow for Retrieval Augmented Generation, 第9页, RAG-Critic: Leveraging Automated Critic-Guided Agentic Workflow for Retrieval Augmented Generation_chunk_047]</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人类专家在15分钟时间限制下的准确率为53.7%。
+来自: [LongBench v2: Towards Deeper Understanding and Reasoning on Realistic Long-context Multitasks, 第1页, LongBench v2: Towards Deeper Understanding and Reasoning on Realistic Long-context Multitasks_chunk_001]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -598,7 +744,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -619,6 +765,28 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="161"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cambria Math"/>
+      <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -998,7 +1166,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="42" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>160</v>
+        <v>118</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1043,7 +1211,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="252" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -1054,7 +1222,7 @@
         <v>16</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>119</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
@@ -1087,62 +1255,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="238" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="210" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="4">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1</v>
+      </c>
+      <c r="K3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="252" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2">
-        <v>1</v>
-      </c>
-      <c r="G3" s="2">
-        <v>1</v>
-      </c>
-      <c r="H3" s="2">
-        <v>1</v>
-      </c>
-      <c r="I3" s="4">
-        <v>1</v>
-      </c>
-      <c r="J3" s="2">
-        <v>1</v>
-      </c>
-      <c r="K3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" s="2">
-        <v>1</v>
-      </c>
-      <c r="M3" s="2">
-        <v>0</v>
-      </c>
-      <c r="N3" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="322" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>129</v>
       </c>
       <c r="E4" s="2">
         <v>1</v>
@@ -1175,18 +1343,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="336" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="238" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
@@ -1219,18 +1387,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="252" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>29</v>
+        <v>131</v>
       </c>
       <c r="E6" s="2">
         <v>0</v>
@@ -1245,7 +1413,7 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="I6" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="2">
         <v>0.85699999999999998</v>
@@ -1263,18 +1431,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="252" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="E7" s="2">
         <v>1</v>
@@ -1307,18 +1475,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="308" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>35</v>
+        <v>133</v>
       </c>
       <c r="E8" s="2">
         <v>1</v>
@@ -1353,16 +1521,16 @@
     </row>
     <row r="9" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>38</v>
+        <v>134</v>
       </c>
       <c r="E9" s="2">
         <v>1</v>
@@ -1397,16 +1565,16 @@
     </row>
     <row r="10" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>41</v>
+        <v>135</v>
       </c>
       <c r="E10" s="2">
         <v>1</v>
@@ -1439,18 +1607,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="266" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>44</v>
+        <v>136</v>
       </c>
       <c r="E11" s="2">
         <v>1</v>
@@ -1483,18 +1651,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="322" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="252" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>47</v>
+        <v>137</v>
       </c>
       <c r="E12" s="2">
         <v>1</v>
@@ -1527,18 +1695,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="392" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
       <c r="E13" s="2">
         <v>1</v>
@@ -1571,18 +1739,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="252" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="224" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>54</v>
+        <v>139</v>
       </c>
       <c r="E14" s="2">
         <v>1</v>
@@ -1617,16 +1785,16 @@
     </row>
     <row r="15" spans="1:15" ht="224" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>57</v>
+        <v>122</v>
       </c>
       <c r="E15" s="2">
         <v>1</v>
@@ -1659,18 +1827,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="336" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="E16" s="2">
         <v>1</v>
@@ -1705,16 +1873,16 @@
     </row>
     <row r="17" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>63</v>
+        <v>141</v>
       </c>
       <c r="E17" s="2">
         <v>0</v>
@@ -1747,18 +1915,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="364" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>66</v>
+        <v>142</v>
       </c>
       <c r="E18" s="2">
         <v>1</v>
@@ -1791,18 +1959,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="308" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="E19" s="2">
         <v>0</v>
@@ -1835,18 +2003,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="392" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="295" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="D20" s="2" t="s">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="E20" s="2">
         <v>1</v>
@@ -1881,16 +2049,16 @@
     </row>
     <row r="21" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>75</v>
+        <v>145</v>
       </c>
       <c r="E21" s="2">
         <v>1</v>
@@ -1925,16 +2093,16 @@
     </row>
     <row r="22" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="E22" s="2">
         <v>1</v>
@@ -1967,18 +2135,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="266" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="E23" s="2">
         <v>1</v>
@@ -2011,18 +2179,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="252" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>84</v>
+        <v>148</v>
       </c>
       <c r="E24" s="2">
         <v>1</v>
@@ -2055,18 +2223,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="280" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>88</v>
+        <v>149</v>
       </c>
       <c r="E25" s="2">
         <v>1</v>
@@ -2099,18 +2267,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="280" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="E26" s="2">
         <v>1</v>
@@ -2145,16 +2313,16 @@
     </row>
     <row r="27" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>94</v>
+        <v>151</v>
       </c>
       <c r="E27" s="2">
         <v>1</v>
@@ -2187,18 +2355,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="350" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="140" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="E28" s="2">
         <v>1</v>
@@ -2231,18 +2399,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="280" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="238" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="E29" s="2">
         <v>1</v>
@@ -2275,18 +2443,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="406" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" ht="294" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>103</v>
+        <v>152</v>
       </c>
       <c r="E30" s="2">
         <v>1</v>
@@ -2319,18 +2487,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" ht="210" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="E31" s="2">
         <v>1</v>
@@ -2363,18 +2531,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="406" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="E32" s="2">
         <v>1</v>
@@ -2389,7 +2557,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J32" s="2">
         <v>1</v>
@@ -2409,16 +2577,16 @@
     </row>
     <row r="33" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>112</v>
+        <v>153</v>
       </c>
       <c r="E33" s="2">
         <v>1</v>
@@ -2453,16 +2621,16 @@
     </row>
     <row r="34" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>115</v>
+        <v>154</v>
       </c>
       <c r="E34" s="2">
         <v>1</v>
@@ -2495,18 +2663,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="294" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" ht="210" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="E35" s="2">
         <v>1</v>
@@ -2541,16 +2709,16 @@
     </row>
     <row r="36" spans="1:15" ht="308" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E36" s="2">
         <v>0</v>
@@ -2585,16 +2753,16 @@
     </row>
     <row r="37" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="E37" s="2">
         <v>0</v>
@@ -2629,16 +2797,16 @@
     </row>
     <row r="38" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>126</v>
+        <v>89</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>127</v>
+        <v>90</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="E38" s="2">
         <v>0</v>
@@ -2671,18 +2839,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:15" s="5" customFormat="1" ht="350" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" s="5" customFormat="1" ht="154" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>130</v>
+        <v>92</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="E39" s="5">
         <v>0</v>
@@ -2715,18 +2883,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" ht="378" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>132</v>
+        <v>94</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E40" s="2">
         <v>1</v>
@@ -2761,16 +2929,16 @@
     </row>
     <row r="41" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="E41" s="2">
         <v>1</v>
@@ -2785,7 +2953,7 @@
         <v>1</v>
       </c>
       <c r="I41" s="4">
-        <v>1</v>
+        <v>0.66700000000000004</v>
       </c>
       <c r="J41" s="2">
         <v>0.8</v>
@@ -2805,16 +2973,16 @@
     </row>
     <row r="42" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="E42" s="2">
         <v>0</v>
@@ -2849,16 +3017,16 @@
     </row>
     <row r="43" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="E43" s="2">
         <v>0</v>
@@ -2891,18 +3059,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="112" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" ht="56" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="J44" s="2">
         <v>1</v>
@@ -2923,18 +3091,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="140" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" ht="70" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>147</v>
+        <v>105</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="J45" s="2">
         <v>1</v>
@@ -2955,18 +3123,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="84" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" ht="42" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="J46" s="2">
         <v>1</v>
@@ -2987,18 +3155,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="210" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" ht="84" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="J47" s="2">
         <v>1</v>
@@ -3019,18 +3187,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="98" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" ht="42" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="J48" s="2">
         <v>1</v>
@@ -3051,18 +3219,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="98" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" ht="56" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>151</v>
+        <v>109</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="J49" s="2">
         <v>1</v>
@@ -3083,18 +3251,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="126" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" ht="56" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="J50" s="2">
         <v>1</v>
@@ -3115,18 +3283,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="126" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" ht="56" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>153</v>
+        <v>111</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="J51" s="2">
         <v>1</v>
@@ -3147,9 +3315,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="28" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="E53" s="2">
         <f>AVERAGEIFS(E2:E51,K2:K51,FALSE)</f>
@@ -3169,7 +3337,7 @@
       </c>
       <c r="I53" s="4">
         <f>AVERAGEIFS(I2:I51,K2:K51,FALSE)</f>
-        <v>0.88493571428571438</v>
+        <v>0.91272142857142868</v>
       </c>
       <c r="J53" s="2">
         <f>AVERAGE(J2:J51)</f>
@@ -3188,9 +3356,9 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="28" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>155</v>
+        <v>113</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
@@ -3213,7 +3381,7 @@
       </c>
       <c r="I54" s="4">
         <f>AVERAGEIFS(I2:I51,B2:B51,"定义类",K2:K51,FALSE)</f>
-        <v>0.91666666666666663</v>
+        <v>1</v>
       </c>
       <c r="J54" s="2">
         <f>AVERAGEIF(B2:B51,"定义类",J2:J51)</f>
@@ -3232,12 +3400,12 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="42" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" ht="28" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E55" s="2">
         <f>AVERAGEIFS(E2:E51,B2:B51,"方法细节类",K2:K51,FALSE)</f>
@@ -3276,12 +3444,12 @@
         <v>0.18181818181818182</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="42" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" ht="28" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="E56" s="2">
         <f>AVERAGEIFS(E2:E51,B2:B51,"实验结果类",K2:K51,FALSE)</f>
@@ -3301,7 +3469,7 @@
       </c>
       <c r="I56" s="4">
         <f>AVERAGEIFS(I2:I51,B2:B51,"实验结果类",K2:K51,FALSE)</f>
-        <v>0.95454545454545459</v>
+        <v>1</v>
       </c>
       <c r="J56" s="2">
         <f>AVERAGEIF(B2:B51,"实验结果类",J2:J51)</f>
@@ -3320,12 +3488,12 @@
         <v>0.18181818181818182</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="42" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" ht="28" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="E57" s="2">
         <f>AVERAGEIFS(E2:E51,B2:B51,"跨论文比较类",K2:K51,FALSE)</f>
@@ -3345,7 +3513,7 @@
       </c>
       <c r="I57" s="4">
         <f>AVERAGEIFS(I2:I51,B2:B51,"跨论文比较类",K2:K51,FALSE)</f>
-        <v>0.7084125</v>
+        <v>0.66678749999999998</v>
       </c>
       <c r="J57" s="2">
         <f>AVERAGEIF(B2:B51,"跨论文比较类",J2:J51)</f>
@@ -3364,12 +3532,12 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="42" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" ht="28" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="E58" s="2" t="e">
         <f>AVERAGEIFS(E2:E51,B2:B51,"不可回答类",K2:K51,FALSE)</f>

--- a/code/experiment/256chunk_BGE-M3_5topk_Y.xlsx
+++ b/code/experiment/256chunk_BGE-M3_5topk_Y.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rag_project\code\experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C786848-6F2C-4315-9757-88C527CA70F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51EF40F3-D837-4457-A900-268EF21912D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -199,9 +199,6 @@
   </si>
   <si>
     <t>α参数的最优范围在0.65到0.8之间。这个参数用于平衡工具描述和参数描述在工具检索中的权重。</t>
-  </si>
-  <si>
-    <t>CypherBench 是如何从 RDF 图生成领域特定属性图的？</t>
   </si>
   <si>
     <t>CypherBench 通过将 RDF 图转换为多个领域特定的属性图（domain-specific property graphs）来实现这一过程，并使用 Cypher 语言对其进行查询。</t>
@@ -737,6 +734,10 @@
   <si>
     <t>人类专家在15分钟时间限制下的准确率为53.7%。
 来自: [LongBench v2: Towards Deeper Understanding and Reasoning on Realistic Long-context Multitasks, 第1页, LongBench v2: Towards Deeper Understanding and Reasoning on Realistic Long-context Multitasks_chunk_001]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CypherBench 提出了什么核心方法来应对 RDF 查询的挑战？</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1166,7 +1167,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="42" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1222,7 +1223,7 @@
         <v>16</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
@@ -1266,7 +1267,7 @@
         <v>18</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E3" s="2">
         <v>1</v>
@@ -1310,7 +1311,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E4" s="2">
         <v>1</v>
@@ -1354,7 +1355,7 @@
         <v>22</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
@@ -1398,7 +1399,7 @@
         <v>24</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E6" s="2">
         <v>0</v>
@@ -1442,7 +1443,7 @@
         <v>26</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E7" s="2">
         <v>1</v>
@@ -1486,7 +1487,7 @@
         <v>28</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E8" s="2">
         <v>1</v>
@@ -1530,7 +1531,7 @@
         <v>30</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E9" s="2">
         <v>1</v>
@@ -1574,7 +1575,7 @@
         <v>32</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E10" s="2">
         <v>1</v>
@@ -1618,7 +1619,7 @@
         <v>34</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E11" s="2">
         <v>1</v>
@@ -1662,7 +1663,7 @@
         <v>36</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E12" s="2">
         <v>1</v>
@@ -1706,7 +1707,7 @@
         <v>38</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E13" s="2">
         <v>1</v>
@@ -1750,7 +1751,7 @@
         <v>41</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E14" s="2">
         <v>1</v>
@@ -1783,7 +1784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="224" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>42</v>
       </c>
@@ -1794,7 +1795,7 @@
         <v>43</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E15" s="2">
         <v>1</v>
@@ -1838,7 +1839,7 @@
         <v>45</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E16" s="2">
         <v>1</v>
@@ -1882,7 +1883,7 @@
         <v>47</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E17" s="2">
         <v>0</v>
@@ -1926,7 +1927,7 @@
         <v>49</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E18" s="2">
         <v>1</v>
@@ -1970,7 +1971,7 @@
         <v>51</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E19" s="2">
         <v>0</v>
@@ -2005,7 +2006,7 @@
     </row>
     <row r="20" spans="1:14" ht="295" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>40</v>
@@ -2014,7 +2015,7 @@
         <v>52</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E20" s="2">
         <v>1</v>
@@ -2049,16 +2050,16 @@
     </row>
     <row r="21" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E21" s="2">
         <v>1</v>
@@ -2093,16 +2094,16 @@
     </row>
     <row r="22" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E22" s="2">
         <v>1</v>
@@ -2137,16 +2138,16 @@
     </row>
     <row r="23" spans="1:14" ht="266" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E23" s="2">
         <v>1</v>
@@ -2181,16 +2182,16 @@
     </row>
     <row r="24" spans="1:14" ht="252" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E24" s="2">
         <v>1</v>
@@ -2225,16 +2226,16 @@
     </row>
     <row r="25" spans="1:14" ht="280" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="D25" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E25" s="2">
         <v>1</v>
@@ -2269,16 +2270,16 @@
     </row>
     <row r="26" spans="1:14" ht="280" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="D26" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E26" s="2">
         <v>1</v>
@@ -2313,16 +2314,16 @@
     </row>
     <row r="27" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="D27" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E27" s="2">
         <v>1</v>
@@ -2355,18 +2356,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="140" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="196" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="D28" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E28" s="2">
         <v>1</v>
@@ -2401,16 +2402,16 @@
     </row>
     <row r="29" spans="1:14" ht="238" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="D29" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E29" s="2">
         <v>1</v>
@@ -2445,16 +2446,16 @@
     </row>
     <row r="30" spans="1:14" ht="294" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="D30" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E30" s="2">
         <v>1</v>
@@ -2487,18 +2488,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="210" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" ht="322" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E31" s="2">
         <v>1</v>
@@ -2531,18 +2532,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="406" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="D32" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E32" s="2">
         <v>1</v>
@@ -2577,16 +2578,16 @@
     </row>
     <row r="33" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="D33" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E33" s="2">
         <v>1</v>
@@ -2621,16 +2622,16 @@
     </row>
     <row r="34" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="D34" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E34" s="2">
         <v>1</v>
@@ -2665,16 +2666,16 @@
     </row>
     <row r="35" spans="1:15" ht="210" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="D35" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E35" s="2">
         <v>1</v>
@@ -2707,18 +2708,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="308" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="D36" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E36" s="2">
         <v>0</v>
@@ -2753,16 +2754,16 @@
     </row>
     <row r="37" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="D37" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E37" s="2">
         <v>0</v>
@@ -2797,16 +2798,16 @@
     </row>
     <row r="38" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="D38" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E38" s="2">
         <v>0</v>
@@ -2841,16 +2842,16 @@
     </row>
     <row r="39" spans="1:15" s="5" customFormat="1" ht="154" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C39" s="5" t="s">
+      <c r="D39" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>93</v>
       </c>
       <c r="E39" s="5">
         <v>0</v>
@@ -2883,18 +2884,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="378" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="D40" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E40" s="2">
         <v>1</v>
@@ -2929,16 +2930,16 @@
     </row>
     <row r="41" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="D41" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E41" s="2">
         <v>1</v>
@@ -2973,16 +2974,16 @@
     </row>
     <row r="42" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="D42" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E42" s="2">
         <v>0</v>
@@ -3017,16 +3018,16 @@
     </row>
     <row r="43" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="D43" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E43" s="2">
         <v>0</v>
@@ -3061,16 +3062,16 @@
     </row>
     <row r="44" spans="1:15" ht="56" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="D44" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J44" s="2">
         <v>1</v>
@@ -3093,16 +3094,16 @@
     </row>
     <row r="45" spans="1:15" ht="70" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="D45" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J45" s="2">
         <v>1</v>
@@ -3125,16 +3126,16 @@
     </row>
     <row r="46" spans="1:15" ht="42" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="D46" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J46" s="2">
         <v>1</v>
@@ -3157,16 +3158,16 @@
     </row>
     <row r="47" spans="1:15" ht="84" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="D47" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J47" s="2">
         <v>1</v>
@@ -3189,16 +3190,16 @@
     </row>
     <row r="48" spans="1:15" ht="42" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="D48" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J48" s="2">
         <v>1</v>
@@ -3221,16 +3222,16 @@
     </row>
     <row r="49" spans="1:15" ht="56" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="D49" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J49" s="2">
         <v>1</v>
@@ -3253,16 +3254,16 @@
     </row>
     <row r="50" spans="1:15" ht="56" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="D50" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J50" s="2">
         <v>1</v>
@@ -3285,16 +3286,16 @@
     </row>
     <row r="51" spans="1:15" ht="56" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="D51" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J51" s="2">
         <v>1</v>
@@ -3317,7 +3318,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E53" s="2">
         <f>AVERAGEIFS(E2:E51,K2:K51,FALSE)</f>
@@ -3358,7 +3359,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
@@ -3402,7 +3403,7 @@
     </row>
     <row r="55" spans="1:15" ht="28" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>40</v>
@@ -3446,10 +3447,10 @@
     </row>
     <row r="56" spans="1:15" ht="28" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E56" s="2">
         <f>AVERAGEIFS(E2:E51,B2:B51,"实验结果类",K2:K51,FALSE)</f>
@@ -3490,10 +3491,10 @@
     </row>
     <row r="57" spans="1:15" ht="28" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E57" s="2">
         <f>AVERAGEIFS(E2:E51,B2:B51,"跨论文比较类",K2:K51,FALSE)</f>
@@ -3534,10 +3535,10 @@
     </row>
     <row r="58" spans="1:15" ht="28" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E58" s="2" t="e">
         <f>AVERAGEIFS(E2:E51,B2:B51,"不可回答类",K2:K51,FALSE)</f>
